--- a/artfynd/A 27724-2026 artfynd.xlsx
+++ b/artfynd/A 27724-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135023647</v>
+        <v>135032570</v>
       </c>
       <c r="B2" t="n">
         <v>57162</v>
@@ -703,32 +703,39 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497636</v>
+        <v>497665</v>
       </c>
       <c r="R2" t="n">
-        <v>6621917</v>
+        <v>6621899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,38 +785,23 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135032570</v>
+        <v>135033089</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -844,7 +841,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -858,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497665</v>
+        <v>497769</v>
       </c>
       <c r="R3" t="n">
-        <v>6621899</v>
+        <v>6621851</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -893,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033089</v>
+        <v>135033156</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -958,24 +960,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497769</v>
+        <v>497764</v>
       </c>
       <c r="R4" t="n">
-        <v>6621851</v>
+        <v>6621865</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1019,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,7 +1044,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033156</v>
+        <v>135033232</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1092,7 +1075,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1101,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497764</v>
+        <v>497781</v>
       </c>
       <c r="R5" t="n">
-        <v>6621865</v>
+        <v>6621879</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1136,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning på hällen under stor tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135033232</v>
+        <v>135032906</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,39 +1172,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497781</v>
+        <v>497759</v>
       </c>
       <c r="R6" t="n">
-        <v>6621879</v>
+        <v>6621852</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1248,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning på hällen under stor tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,118 +1270,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135032906</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8449</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>497759</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6621852</v>
-      </c>
-      <c r="S7" t="n">
-        <v>20</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27724-2026 artfynd.xlsx
+++ b/artfynd/A 27724-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135032570</v>
+        <v>135023647</v>
       </c>
       <c r="B2" t="n">
         <v>57162</v>
@@ -703,39 +703,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497665</v>
+        <v>497636</v>
       </c>
       <c r="R2" t="n">
-        <v>6621899</v>
+        <v>6621917</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,23 +773,38 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135033089</v>
+        <v>135032570</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -841,7 +844,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -855,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497769</v>
+        <v>497665</v>
       </c>
       <c r="R3" t="n">
-        <v>6621851</v>
+        <v>6621899</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -890,7 +893,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +903,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +930,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033156</v>
+        <v>135033089</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -960,10 +958,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497764</v>
+        <v>497769</v>
       </c>
       <c r="R4" t="n">
-        <v>6621865</v>
+        <v>6621851</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1007,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033232</v>
+        <v>135033156</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1075,7 +1092,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497781</v>
+        <v>497764</v>
       </c>
       <c r="R5" t="n">
-        <v>6621879</v>
+        <v>6621865</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1119,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning på hällen under stor tall.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135032906</v>
+        <v>135033232</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,39 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497759</v>
+        <v>497781</v>
       </c>
       <c r="R6" t="n">
-        <v>6621852</v>
+        <v>6621879</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1236,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning på hällen under stor tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,6 +1287,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135032906</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497759</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6621852</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27724-2026 artfynd.xlsx
+++ b/artfynd/A 27724-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,10 +672,15 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135023647</v>
+        <v>135032570</v>
       </c>
       <c r="B2" t="n">
         <v>57162</v>
@@ -703,32 +708,39 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497636</v>
+        <v>497665</v>
       </c>
       <c r="R2" t="n">
-        <v>6621917</v>
+        <v>6621899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +764,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,38 +790,28 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135032570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135032570</v>
+        <v>135033089</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -844,7 +851,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -858,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497665</v>
+        <v>497769</v>
       </c>
       <c r="R3" t="n">
-        <v>6621899</v>
+        <v>6621851</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -893,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +910,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +939,15 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033089</v>
+        <v>135033156</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -958,24 +975,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497769</v>
+        <v>497764</v>
       </c>
       <c r="R4" t="n">
-        <v>6621851</v>
+        <v>6621865</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1019,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,10 +1056,15 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033156</v>
+        <v>135033232</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1092,7 +1095,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1101,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497764</v>
+        <v>497781</v>
       </c>
       <c r="R5" t="n">
-        <v>6621865</v>
+        <v>6621879</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1136,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1149,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning på hällen under stor tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,13 +1178,18 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033232</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135033232</v>
+        <v>135032906</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>8449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,39 +1197,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497781</v>
+        <v>497759</v>
       </c>
       <c r="R6" t="n">
-        <v>6621879</v>
+        <v>6621852</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1248,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1271,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning på hällen under stor tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,120 +1295,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135032906</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8449</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>497759</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6621852</v>
-      </c>
-      <c r="S7" t="n">
-        <v>20</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135032906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27724-2026 artfynd.xlsx
+++ b/artfynd/A 27724-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135032570</v>
+        <v>135023647</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,39 +708,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497665</v>
+        <v>497636</v>
       </c>
       <c r="R2" t="n">
-        <v>6621899</v>
+        <v>6621917</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,31 +778,46 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135032570</t>
+          <t>https://artportalen.se/Sighting/135023647</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135033089</v>
+        <v>135032570</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,7 +854,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -865,10 +868,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497769</v>
+        <v>497665</v>
       </c>
       <c r="R3" t="n">
-        <v>6621851</v>
+        <v>6621899</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -900,7 +903,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +913,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjäder och färsk spillning</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,16 +939,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033089</t>
+          <t>https://artportalen.se/Sighting/135032570</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033156</v>
+        <v>135033089</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +973,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -987,10 +999,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497764</v>
+        <v>497769</v>
       </c>
       <c r="R4" t="n">
-        <v>6621865</v>
+        <v>6621851</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1022,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjäder och färsk spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,16 +1075,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033156</t>
+          <t>https://artportalen.se/Sighting/135033089</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033232</v>
+        <v>135033156</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1112,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497781</v>
+        <v>497764</v>
       </c>
       <c r="R5" t="n">
-        <v>6621879</v>
+        <v>6621865</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1139,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,12 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning på hällen under stor tall.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,16 +1192,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033232</t>
+          <t>https://artportalen.se/Sighting/135033156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135032906</v>
+        <v>135033232</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,39 +1209,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497759</v>
+        <v>497781</v>
       </c>
       <c r="R6" t="n">
-        <v>6621852</v>
+        <v>6621879</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1261,7 +1273,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1271,7 +1283,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning på hällen under stor tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,6 +1313,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033232</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135032906</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497759</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6621852</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135032906</t>
         </is>
@@ -1308,6 +1442,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
